--- a/students/Y1S1_course_enrollment_DRC.xlsx
+++ b/students/Y1S1_course_enrollment_DRC.xlsx
@@ -13931,49 +13931,49 @@
       <c r="Y70" s="14" t="inlineStr">
         <is>
           <r>
+            <t xml:space="preserve">0533-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="Z70" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0231-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA70" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0613-102</t>
+          </r>
+        </is>
+      </c>
+      <c r="AB70" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0541-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AC70" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0533-102</t>
+          </r>
+        </is>
+      </c>
+      <c r="AD70" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0613-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AE70" s="14" t="inlineStr">
+        <is>
+          <r>
             <t xml:space="preserve">0222-101</t>
-          </r>
-        </is>
-      </c>
-      <c r="Z70" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0613-101</t>
-          </r>
-        </is>
-      </c>
-      <c r="AA70" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0533-102</t>
-          </r>
-        </is>
-      </c>
-      <c r="AB70" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0541-101</t>
-          </r>
-        </is>
-      </c>
-      <c r="AC70" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0613-102</t>
-          </r>
-        </is>
-      </c>
-      <c r="AD70" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0231-101</t>
-          </r>
-        </is>
-      </c>
-      <c r="AE70" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0533-101</t>
           </r>
         </is>
       </c>
@@ -14127,49 +14127,49 @@
       <c r="Y71" s="14" t="inlineStr">
         <is>
           <r>
+            <t xml:space="preserve">0541-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="Z71" s="14" t="inlineStr">
+        <is>
+          <r>
             <t xml:space="preserve">0533-101</t>
           </r>
         </is>
       </c>
-      <c r="Z71" s="14" t="inlineStr">
+      <c r="AA71" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0231-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AB71" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0613-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AC71" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0613-102</t>
+          </r>
+        </is>
+      </c>
+      <c r="AD71" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0222-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AE71" s="14" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">0533-102</t>
-          </r>
-        </is>
-      </c>
-      <c r="AA71" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0222-101</t>
-          </r>
-        </is>
-      </c>
-      <c r="AB71" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0613-102</t>
-          </r>
-        </is>
-      </c>
-      <c r="AC71" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0613-101</t>
-          </r>
-        </is>
-      </c>
-      <c r="AD71" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0231-101</t>
-          </r>
-        </is>
-      </c>
-      <c r="AE71" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0541-101</t>
           </r>
         </is>
       </c>
@@ -14323,49 +14323,441 @@
       <c r="Y72" s="14" t="inlineStr">
         <is>
           <r>
+            <t xml:space="preserve">0533-102</t>
+          </r>
+        </is>
+      </c>
+      <c r="Z72" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0222-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA72" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0613-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AB72" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0541-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AC72" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0231-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AD72" s="14" t="inlineStr">
+        <is>
+          <r>
             <t xml:space="preserve">0533-101</t>
           </r>
         </is>
       </c>
-      <c r="Z72" s="14" t="inlineStr">
+      <c r="AE72" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0613-102</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="73" customHeight="1" ht="60">
+      <c r="A73" s="12" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">25052801071</t>
+          </r>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">SADNAN SHARIF TAKI</t>
+          </r>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Male</t>
+          </r>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">01992259699</t>
+          </r>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">sadnanshariftaki@gmail.com</t>
+          </r>
+        </is>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">MD. SHORIFUL ALAM</t>
+          </r>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">MASUMA AKTER</t>
+          </r>
+        </is>
+      </c>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">03-03-2002</t>
+          </r>
+        </is>
+      </c>
+      <c r="J73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2024-2025</t>
+          </r>
+        </is>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11th Batch (251 Term)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1st Year 1st Semester</t>
+          </r>
+        </is>
+      </c>
+      <c r="M73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Admission</t>
+          </r>
+        </is>
+      </c>
+      <c r="N73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Regular</t>
+          </r>
+        </is>
+      </c>
+      <c r="O73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Bachelor of Science in Computer Science and Engineering</t>
+          </r>
+        </is>
+      </c>
+      <c r="P73" s="12" t="inlineStr"/>
+      <c r="Q73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Dhaka</t>
+          </r>
+        </is>
+      </c>
+      <c r="R73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Dhaka</t>
+          </r>
+        </is>
+      </c>
+      <c r="S73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Dhaka regional center, BOU</t>
+          </r>
+        </is>
+      </c>
+      <c r="T73" s="12" t="inlineStr"/>
+      <c r="U73" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">https://osapsnew.bou.ac.bd/public/storage/students/52/250/photos/sadnan-sharif-taki_1758178064_photo.jpg</t>
+          </r>
+        </is>
+      </c>
+      <c r="V73" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">[TRX ID: 5XparF0JCnr3zRBm96XznK4KUv0= Payment Date: 17/11/2025 Amount: 14421 ],
+[TRX ID: CII5I1R7VV Payment Date: 18/09/2025 Amount: 1000 ]</t>
+          </r>
+        </is>
+      </c>
+      <c r="W73" s="13" t="n">
+        <v>15421.0</v>
+      </c>
+      <c r="X73" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y73" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0533-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="Z73" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0613-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA73" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0541-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AB73" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0222-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AC73" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0613-102</t>
+          </r>
+        </is>
+      </c>
+      <c r="AD73" s="14" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">0533-102</t>
           </r>
         </is>
       </c>
-      <c r="AA72" s="14" t="inlineStr">
+      <c r="AE73" s="14" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">0231-101</t>
           </r>
         </is>
       </c>
-      <c r="AB72" s="14" t="inlineStr">
+    </row>
+    <row r="74" customHeight="1" ht="60">
+      <c r="A74" s="12" t="n">
+        <v>72.0</v>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">25052801072</t>
+          </r>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">MD. IMRAN HOSSAN</t>
+          </r>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Male</t>
+          </r>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">01686373631</t>
+          </r>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">mdnice5@gmail.com</t>
+          </r>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">MD. BAZLUR RAHMAN</t>
+          </r>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">RAHIMA KHANAM</t>
+          </r>
+        </is>
+      </c>
+      <c r="I74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">25-04-2000</t>
+          </r>
+        </is>
+      </c>
+      <c r="J74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2024-2025</t>
+          </r>
+        </is>
+      </c>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11th Batch (251 Term)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1st Year 1st Semester</t>
+          </r>
+        </is>
+      </c>
+      <c r="M74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Admission</t>
+          </r>
+        </is>
+      </c>
+      <c r="N74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Regular</t>
+          </r>
+        </is>
+      </c>
+      <c r="O74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Bachelor of Science in Computer Science and Engineering</t>
+          </r>
+        </is>
+      </c>
+      <c r="P74" s="12" t="inlineStr"/>
+      <c r="Q74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Dhaka</t>
+          </r>
+        </is>
+      </c>
+      <c r="R74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Dhaka</t>
+          </r>
+        </is>
+      </c>
+      <c r="S74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Dhaka regional center, BOU</t>
+          </r>
+        </is>
+      </c>
+      <c r="T74" s="12" t="inlineStr"/>
+      <c r="U74" s="11" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">https://osapsnew.bou.ac.bd/public/storage/students/52/250/photos/md-imran-hossan_1758177515_photo.jpg</t>
+          </r>
+        </is>
+      </c>
+      <c r="V74" s="12" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">[TRX ID: CJH7CNAMPP Payment Date: 17/10/2025 Amount: 1000 ],
+[TRX ID: MlWOQADES7X97oa495MpCLvsqI8= Payment Date: 15/12/2025 Amount: 14421 ]</t>
+          </r>
+        </is>
+      </c>
+      <c r="W74" s="13" t="n">
+        <v>15421.0</v>
+      </c>
+      <c r="X74" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y74" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0231-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="Z74" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0222-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AA74" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0613-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AB74" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0533-102</t>
+          </r>
+        </is>
+      </c>
+      <c r="AC74" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0541-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AD74" s="14" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">0533-101</t>
+          </r>
+        </is>
+      </c>
+      <c r="AE74" s="14" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">0613-102</t>
-          </r>
-        </is>
-      </c>
-      <c r="AC72" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0541-101</t>
-          </r>
-        </is>
-      </c>
-      <c r="AD72" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0613-101</t>
-          </r>
-        </is>
-      </c>
-      <c r="AE72" s="14" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">0222-101</t>
           </r>
         </is>
       </c>
